--- a/medops/docs/templates/2-设备表.xlsx
+++ b/medops/docs/templates/2-设备表.xlsx
@@ -3257,8 +3257,8 @@
     <cfRule type="duplicateValues" priority="1" dxfId="0" stopIfTrue="0"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 在用 / 停用 / 维修" prompt="留空默认为「在用」" type="list">
-      <formula1>"在用,停用,维修"</formula1>
+    <dataValidation sqref="G2:G301" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 在用 / 维修 / 停用 / 报废" prompt="留空默认为「在用」" type="list">
+      <formula1>"在用,维修,停用,报废"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>在用 / 停用 / 维修 三选一（有下拉可选）。留空默认为「在用」。停用的设备不出现在日常巡检列表里。</t>
+          <t>在用 / 维修 / 停用 / 报废 四选一（有下拉可选）。留空默认为「在用」。只有「在用」的设备出现在日常巡检清单里，其余三种都不出现。</t>
         </is>
       </c>
     </row>

--- a/medops/docs/templates/2-设备表.xlsx
+++ b/medops/docs/templates/2-设备表.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:I301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,8 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -549,6 +551,16 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>有效期</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>提醒提前天数</t>
         </is>
       </c>
     </row>
@@ -560,6 +572,8 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -569,6 +583,8 @@
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -578,6 +594,8 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -587,6 +605,8 @@
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -596,6 +616,8 @@
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -605,6 +627,8 @@
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -614,6 +638,8 @@
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -623,6 +649,8 @@
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -632,6 +660,8 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -641,6 +671,8 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -650,6 +682,8 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -659,6 +693,8 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -668,6 +704,8 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -677,6 +715,8 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -686,6 +726,8 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -695,6 +737,8 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -704,6 +748,8 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -713,6 +759,8 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -722,6 +770,8 @@
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -731,6 +781,8 @@
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -740,6 +792,8 @@
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -749,6 +803,8 @@
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -758,6 +814,8 @@
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -767,6 +825,8 @@
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -776,6 +836,8 @@
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -785,6 +847,8 @@
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -794,6 +858,8 @@
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -803,6 +869,8 @@
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -812,6 +880,8 @@
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -821,6 +891,8 @@
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -830,6 +902,8 @@
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -839,6 +913,8 @@
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -848,6 +924,8 @@
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -857,6 +935,8 @@
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -866,6 +946,8 @@
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -875,6 +957,8 @@
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -884,6 +968,8 @@
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -893,6 +979,8 @@
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -902,6 +990,8 @@
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -911,6 +1001,8 @@
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -920,6 +1012,8 @@
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -929,6 +1023,8 @@
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -938,6 +1034,8 @@
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -947,6 +1045,8 @@
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -956,6 +1056,8 @@
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -965,6 +1067,8 @@
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -974,6 +1078,8 @@
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -983,6 +1089,8 @@
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -992,6 +1100,8 @@
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -1001,6 +1111,8 @@
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1010,6 +1122,8 @@
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -1019,6 +1133,8 @@
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1028,6 +1144,8 @@
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -1037,6 +1155,8 @@
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1046,6 +1166,8 @@
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -1055,6 +1177,8 @@
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1064,6 +1188,8 @@
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+      <c r="I58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -1073,6 +1199,8 @@
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1082,6 +1210,8 @@
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -1091,6 +1221,8 @@
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+      <c r="I61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -1100,6 +1232,8 @@
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -1109,6 +1243,8 @@
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -1118,6 +1254,8 @@
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="I64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -1127,6 +1265,8 @@
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="I65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -1136,6 +1276,8 @@
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -1145,6 +1287,8 @@
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -1154,6 +1298,8 @@
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -1163,6 +1309,8 @@
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -1172,6 +1320,8 @@
       <c r="E70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -1181,6 +1331,8 @@
       <c r="E71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="I71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -1190,6 +1342,8 @@
       <c r="E72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -1199,6 +1353,8 @@
       <c r="E73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -1208,6 +1364,8 @@
       <c r="E74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -1217,6 +1375,8 @@
       <c r="E75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="I75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -1226,6 +1386,8 @@
       <c r="E76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -1235,6 +1397,8 @@
       <c r="E77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -1244,6 +1408,8 @@
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -1253,6 +1419,8 @@
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -1262,6 +1430,8 @@
       <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -1271,6 +1441,8 @@
       <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -1280,6 +1452,8 @@
       <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
       <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -1289,6 +1463,8 @@
       <c r="E83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -1298,6 +1474,8 @@
       <c r="E84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
       <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -1307,6 +1485,8 @@
       <c r="E85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="I85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -1316,6 +1496,8 @@
       <c r="E86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
       <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -1325,6 +1507,8 @@
       <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -1334,6 +1518,8 @@
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -1343,6 +1529,8 @@
       <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -1352,6 +1540,8 @@
       <c r="E90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -1361,6 +1551,8 @@
       <c r="E91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -1370,6 +1562,8 @@
       <c r="E92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -1379,6 +1573,8 @@
       <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -1388,6 +1584,8 @@
       <c r="E94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
       <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -1397,6 +1595,8 @@
       <c r="E95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
       <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -1406,6 +1606,8 @@
       <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -1415,6 +1617,8 @@
       <c r="E97" s="3" t="n"/>
       <c r="F97" s="3" t="n"/>
       <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="I97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -1424,6 +1628,8 @@
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="3" t="n"/>
       <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -1433,6 +1639,8 @@
       <c r="E99" s="3" t="n"/>
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -1442,6 +1650,8 @@
       <c r="E100" s="3" t="n"/>
       <c r="F100" s="3" t="n"/>
       <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -1451,6 +1661,8 @@
       <c r="E101" s="3" t="n"/>
       <c r="F101" s="3" t="n"/>
       <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="I101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -1460,6 +1672,8 @@
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -1469,6 +1683,8 @@
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="n"/>
       <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -1478,6 +1694,8 @@
       <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="n"/>
       <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -1487,6 +1705,8 @@
       <c r="E105" s="3" t="n"/>
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -1496,6 +1716,8 @@
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n"/>
       <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -1505,6 +1727,8 @@
       <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="n"/>
       <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -1514,6 +1738,8 @@
       <c r="E108" s="3" t="n"/>
       <c r="F108" s="3" t="n"/>
       <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -1523,6 +1749,8 @@
       <c r="E109" s="3" t="n"/>
       <c r="F109" s="3" t="n"/>
       <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -1532,6 +1760,8 @@
       <c r="E110" s="3" t="n"/>
       <c r="F110" s="3" t="n"/>
       <c r="G110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -1541,6 +1771,8 @@
       <c r="E111" s="3" t="n"/>
       <c r="F111" s="3" t="n"/>
       <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -1550,6 +1782,8 @@
       <c r="E112" s="3" t="n"/>
       <c r="F112" s="3" t="n"/>
       <c r="G112" s="3" t="n"/>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -1559,6 +1793,8 @@
       <c r="E113" s="3" t="n"/>
       <c r="F113" s="3" t="n"/>
       <c r="G113" s="3" t="n"/>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -1568,6 +1804,8 @@
       <c r="E114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
       <c r="G114" s="3" t="n"/>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -1577,6 +1815,8 @@
       <c r="E115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
       <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -1586,6 +1826,8 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -1595,6 +1837,8 @@
       <c r="E117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="3" t="n"/>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -1604,6 +1848,8 @@
       <c r="E118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -1613,6 +1859,8 @@
       <c r="E119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -1622,6 +1870,8 @@
       <c r="E120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -1631,6 +1881,8 @@
       <c r="E121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="n"/>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -1640,6 +1892,8 @@
       <c r="E122" s="3" t="n"/>
       <c r="F122" s="3" t="n"/>
       <c r="G122" s="3" t="n"/>
+      <c r="H122" s="3" t="n"/>
+      <c r="I122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -1649,6 +1903,8 @@
       <c r="E123" s="3" t="n"/>
       <c r="F123" s="3" t="n"/>
       <c r="G123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -1658,6 +1914,8 @@
       <c r="E124" s="3" t="n"/>
       <c r="F124" s="3" t="n"/>
       <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -1667,6 +1925,8 @@
       <c r="E125" s="3" t="n"/>
       <c r="F125" s="3" t="n"/>
       <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -1676,6 +1936,8 @@
       <c r="E126" s="3" t="n"/>
       <c r="F126" s="3" t="n"/>
       <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -1685,6 +1947,8 @@
       <c r="E127" s="3" t="n"/>
       <c r="F127" s="3" t="n"/>
       <c r="G127" s="3" t="n"/>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -1694,6 +1958,8 @@
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
       <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -1703,6 +1969,8 @@
       <c r="E129" s="3" t="n"/>
       <c r="F129" s="3" t="n"/>
       <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -1712,6 +1980,8 @@
       <c r="E130" s="3" t="n"/>
       <c r="F130" s="3" t="n"/>
       <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -1721,6 +1991,8 @@
       <c r="E131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
+      <c r="I131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -1730,6 +2002,8 @@
       <c r="E132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
       <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -1739,6 +2013,8 @@
       <c r="E133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -1748,6 +2024,8 @@
       <c r="E134" s="3" t="n"/>
       <c r="F134" s="3" t="n"/>
       <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -1757,6 +2035,8 @@
       <c r="E135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -1766,6 +2046,8 @@
       <c r="E136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
       <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -1775,6 +2057,8 @@
       <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
       <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -1784,6 +2068,8 @@
       <c r="E138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -1793,6 +2079,8 @@
       <c r="E139" s="3" t="n"/>
       <c r="F139" s="3" t="n"/>
       <c r="G139" s="3" t="n"/>
+      <c r="H139" s="3" t="n"/>
+      <c r="I139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -1802,6 +2090,8 @@
       <c r="E140" s="3" t="n"/>
       <c r="F140" s="3" t="n"/>
       <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
+      <c r="I140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -1811,6 +2101,8 @@
       <c r="E141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -1820,6 +2112,8 @@
       <c r="E142" s="3" t="n"/>
       <c r="F142" s="3" t="n"/>
       <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -1829,6 +2123,8 @@
       <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
       <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
+      <c r="I143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -1838,6 +2134,8 @@
       <c r="E144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
       <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -1847,6 +2145,8 @@
       <c r="E145" s="3" t="n"/>
       <c r="F145" s="3" t="n"/>
       <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -1856,6 +2156,8 @@
       <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
       <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -1865,6 +2167,8 @@
       <c r="E147" s="3" t="n"/>
       <c r="F147" s="3" t="n"/>
       <c r="G147" s="3" t="n"/>
+      <c r="H147" s="3" t="n"/>
+      <c r="I147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -1874,6 +2178,8 @@
       <c r="E148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
+      <c r="I148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -1883,6 +2189,8 @@
       <c r="E149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
+      <c r="H149" s="3" t="n"/>
+      <c r="I149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -1892,6 +2200,8 @@
       <c r="E150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -1901,6 +2211,8 @@
       <c r="E151" s="3" t="n"/>
       <c r="F151" s="3" t="n"/>
       <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="n"/>
+      <c r="I151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -1910,6 +2222,8 @@
       <c r="E152" s="3" t="n"/>
       <c r="F152" s="3" t="n"/>
       <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -1919,6 +2233,8 @@
       <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -1928,6 +2244,8 @@
       <c r="E154" s="3" t="n"/>
       <c r="F154" s="3" t="n"/>
       <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -1937,6 +2255,8 @@
       <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
       <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
+      <c r="I155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -1946,6 +2266,8 @@
       <c r="E156" s="3" t="n"/>
       <c r="F156" s="3" t="n"/>
       <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
+      <c r="I156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -1955,6 +2277,8 @@
       <c r="E157" s="3" t="n"/>
       <c r="F157" s="3" t="n"/>
       <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
+      <c r="I157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -1964,6 +2288,8 @@
       <c r="E158" s="3" t="n"/>
       <c r="F158" s="3" t="n"/>
       <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -1973,6 +2299,8 @@
       <c r="E159" s="3" t="n"/>
       <c r="F159" s="3" t="n"/>
       <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -1982,6 +2310,8 @@
       <c r="E160" s="3" t="n"/>
       <c r="F160" s="3" t="n"/>
       <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -1991,6 +2321,8 @@
       <c r="E161" s="3" t="n"/>
       <c r="F161" s="3" t="n"/>
       <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="n"/>
+      <c r="I161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -2000,6 +2332,8 @@
       <c r="E162" s="3" t="n"/>
       <c r="F162" s="3" t="n"/>
       <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -2009,6 +2343,8 @@
       <c r="E163" s="3" t="n"/>
       <c r="F163" s="3" t="n"/>
       <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="n"/>
+      <c r="I163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -2018,6 +2354,8 @@
       <c r="E164" s="3" t="n"/>
       <c r="F164" s="3" t="n"/>
       <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -2027,6 +2365,8 @@
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
       <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -2036,6 +2376,8 @@
       <c r="E166" s="3" t="n"/>
       <c r="F166" s="3" t="n"/>
       <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -2045,6 +2387,8 @@
       <c r="E167" s="3" t="n"/>
       <c r="F167" s="3" t="n"/>
       <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -2054,6 +2398,8 @@
       <c r="E168" s="3" t="n"/>
       <c r="F168" s="3" t="n"/>
       <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -2063,6 +2409,8 @@
       <c r="E169" s="3" t="n"/>
       <c r="F169" s="3" t="n"/>
       <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -2072,6 +2420,8 @@
       <c r="E170" s="3" t="n"/>
       <c r="F170" s="3" t="n"/>
       <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -2081,6 +2431,8 @@
       <c r="E171" s="3" t="n"/>
       <c r="F171" s="3" t="n"/>
       <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -2090,6 +2442,8 @@
       <c r="E172" s="3" t="n"/>
       <c r="F172" s="3" t="n"/>
       <c r="G172" s="3" t="n"/>
+      <c r="H172" s="3" t="n"/>
+      <c r="I172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -2099,6 +2453,8 @@
       <c r="E173" s="3" t="n"/>
       <c r="F173" s="3" t="n"/>
       <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -2108,6 +2464,8 @@
       <c r="E174" s="3" t="n"/>
       <c r="F174" s="3" t="n"/>
       <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -2117,6 +2475,8 @@
       <c r="E175" s="3" t="n"/>
       <c r="F175" s="3" t="n"/>
       <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -2126,6 +2486,8 @@
       <c r="E176" s="3" t="n"/>
       <c r="F176" s="3" t="n"/>
       <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="n"/>
+      <c r="I176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -2135,6 +2497,8 @@
       <c r="E177" s="3" t="n"/>
       <c r="F177" s="3" t="n"/>
       <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -2144,6 +2508,8 @@
       <c r="E178" s="3" t="n"/>
       <c r="F178" s="3" t="n"/>
       <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -2153,6 +2519,8 @@
       <c r="E179" s="3" t="n"/>
       <c r="F179" s="3" t="n"/>
       <c r="G179" s="3" t="n"/>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -2162,6 +2530,8 @@
       <c r="E180" s="3" t="n"/>
       <c r="F180" s="3" t="n"/>
       <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -2171,6 +2541,8 @@
       <c r="E181" s="3" t="n"/>
       <c r="F181" s="3" t="n"/>
       <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -2180,6 +2552,8 @@
       <c r="E182" s="3" t="n"/>
       <c r="F182" s="3" t="n"/>
       <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -2189,6 +2563,8 @@
       <c r="E183" s="3" t="n"/>
       <c r="F183" s="3" t="n"/>
       <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -2198,6 +2574,8 @@
       <c r="E184" s="3" t="n"/>
       <c r="F184" s="3" t="n"/>
       <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -2207,6 +2585,8 @@
       <c r="E185" s="3" t="n"/>
       <c r="F185" s="3" t="n"/>
       <c r="G185" s="3" t="n"/>
+      <c r="H185" s="3" t="n"/>
+      <c r="I185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -2216,6 +2596,8 @@
       <c r="E186" s="3" t="n"/>
       <c r="F186" s="3" t="n"/>
       <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -2225,6 +2607,8 @@
       <c r="E187" s="3" t="n"/>
       <c r="F187" s="3" t="n"/>
       <c r="G187" s="3" t="n"/>
+      <c r="H187" s="3" t="n"/>
+      <c r="I187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -2234,6 +2618,8 @@
       <c r="E188" s="3" t="n"/>
       <c r="F188" s="3" t="n"/>
       <c r="G188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
+      <c r="I188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -2243,6 +2629,8 @@
       <c r="E189" s="3" t="n"/>
       <c r="F189" s="3" t="n"/>
       <c r="G189" s="3" t="n"/>
+      <c r="H189" s="3" t="n"/>
+      <c r="I189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -2252,6 +2640,8 @@
       <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="n"/>
       <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -2261,6 +2651,8 @@
       <c r="E191" s="3" t="n"/>
       <c r="F191" s="3" t="n"/>
       <c r="G191" s="3" t="n"/>
+      <c r="H191" s="3" t="n"/>
+      <c r="I191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -2270,6 +2662,8 @@
       <c r="E192" s="3" t="n"/>
       <c r="F192" s="3" t="n"/>
       <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -2279,6 +2673,8 @@
       <c r="E193" s="3" t="n"/>
       <c r="F193" s="3" t="n"/>
       <c r="G193" s="3" t="n"/>
+      <c r="H193" s="3" t="n"/>
+      <c r="I193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -2288,6 +2684,8 @@
       <c r="E194" s="3" t="n"/>
       <c r="F194" s="3" t="n"/>
       <c r="G194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -2297,6 +2695,8 @@
       <c r="E195" s="3" t="n"/>
       <c r="F195" s="3" t="n"/>
       <c r="G195" s="3" t="n"/>
+      <c r="H195" s="3" t="n"/>
+      <c r="I195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -2306,6 +2706,8 @@
       <c r="E196" s="3" t="n"/>
       <c r="F196" s="3" t="n"/>
       <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -2315,6 +2717,8 @@
       <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
       <c r="G197" s="3" t="n"/>
+      <c r="H197" s="3" t="n"/>
+      <c r="I197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -2324,6 +2728,8 @@
       <c r="E198" s="3" t="n"/>
       <c r="F198" s="3" t="n"/>
       <c r="G198" s="3" t="n"/>
+      <c r="H198" s="3" t="n"/>
+      <c r="I198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -2333,6 +2739,8 @@
       <c r="E199" s="3" t="n"/>
       <c r="F199" s="3" t="n"/>
       <c r="G199" s="3" t="n"/>
+      <c r="H199" s="3" t="n"/>
+      <c r="I199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -2342,6 +2750,8 @@
       <c r="E200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
+      <c r="H200" s="3" t="n"/>
+      <c r="I200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -2351,6 +2761,8 @@
       <c r="E201" s="3" t="n"/>
       <c r="F201" s="3" t="n"/>
       <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -2360,6 +2772,8 @@
       <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
       <c r="G202" s="3" t="n"/>
+      <c r="H202" s="3" t="n"/>
+      <c r="I202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n"/>
@@ -2369,6 +2783,8 @@
       <c r="E203" s="3" t="n"/>
       <c r="F203" s="3" t="n"/>
       <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n"/>
@@ -2378,6 +2794,8 @@
       <c r="E204" s="3" t="n"/>
       <c r="F204" s="3" t="n"/>
       <c r="G204" s="3" t="n"/>
+      <c r="H204" s="3" t="n"/>
+      <c r="I204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n"/>
@@ -2387,6 +2805,8 @@
       <c r="E205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
       <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n"/>
@@ -2396,6 +2816,8 @@
       <c r="E206" s="3" t="n"/>
       <c r="F206" s="3" t="n"/>
       <c r="G206" s="3" t="n"/>
+      <c r="H206" s="3" t="n"/>
+      <c r="I206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n"/>
@@ -2405,6 +2827,8 @@
       <c r="E207" s="3" t="n"/>
       <c r="F207" s="3" t="n"/>
       <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n"/>
@@ -2414,6 +2838,8 @@
       <c r="E208" s="3" t="n"/>
       <c r="F208" s="3" t="n"/>
       <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n"/>
@@ -2423,6 +2849,8 @@
       <c r="E209" s="3" t="n"/>
       <c r="F209" s="3" t="n"/>
       <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n"/>
@@ -2432,6 +2860,8 @@
       <c r="E210" s="3" t="n"/>
       <c r="F210" s="3" t="n"/>
       <c r="G210" s="3" t="n"/>
+      <c r="H210" s="3" t="n"/>
+      <c r="I210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n"/>
@@ -2441,6 +2871,8 @@
       <c r="E211" s="3" t="n"/>
       <c r="F211" s="3" t="n"/>
       <c r="G211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
+      <c r="I211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n"/>
@@ -2450,6 +2882,8 @@
       <c r="E212" s="3" t="n"/>
       <c r="F212" s="3" t="n"/>
       <c r="G212" s="3" t="n"/>
+      <c r="H212" s="3" t="n"/>
+      <c r="I212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n"/>
@@ -2459,6 +2893,8 @@
       <c r="E213" s="3" t="n"/>
       <c r="F213" s="3" t="n"/>
       <c r="G213" s="3" t="n"/>
+      <c r="H213" s="3" t="n"/>
+      <c r="I213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n"/>
@@ -2468,6 +2904,8 @@
       <c r="E214" s="3" t="n"/>
       <c r="F214" s="3" t="n"/>
       <c r="G214" s="3" t="n"/>
+      <c r="H214" s="3" t="n"/>
+      <c r="I214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n"/>
@@ -2477,6 +2915,8 @@
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="n"/>
       <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n"/>
@@ -2486,6 +2926,8 @@
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3" t="n"/>
       <c r="G216" s="3" t="n"/>
+      <c r="H216" s="3" t="n"/>
+      <c r="I216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n"/>
@@ -2495,6 +2937,8 @@
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
       <c r="G217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
+      <c r="I217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n"/>
@@ -2504,6 +2948,8 @@
       <c r="E218" s="3" t="n"/>
       <c r="F218" s="3" t="n"/>
       <c r="G218" s="3" t="n"/>
+      <c r="H218" s="3" t="n"/>
+      <c r="I218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n"/>
@@ -2513,6 +2959,8 @@
       <c r="E219" s="3" t="n"/>
       <c r="F219" s="3" t="n"/>
       <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
+      <c r="I219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n"/>
@@ -2522,6 +2970,8 @@
       <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
       <c r="G220" s="3" t="n"/>
+      <c r="H220" s="3" t="n"/>
+      <c r="I220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n"/>
@@ -2531,6 +2981,8 @@
       <c r="E221" s="3" t="n"/>
       <c r="F221" s="3" t="n"/>
       <c r="G221" s="3" t="n"/>
+      <c r="H221" s="3" t="n"/>
+      <c r="I221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n"/>
@@ -2540,6 +2992,8 @@
       <c r="E222" s="3" t="n"/>
       <c r="F222" s="3" t="n"/>
       <c r="G222" s="3" t="n"/>
+      <c r="H222" s="3" t="n"/>
+      <c r="I222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n"/>
@@ -2549,6 +3003,8 @@
       <c r="E223" s="3" t="n"/>
       <c r="F223" s="3" t="n"/>
       <c r="G223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
+      <c r="I223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n"/>
@@ -2558,6 +3014,8 @@
       <c r="E224" s="3" t="n"/>
       <c r="F224" s="3" t="n"/>
       <c r="G224" s="3" t="n"/>
+      <c r="H224" s="3" t="n"/>
+      <c r="I224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n"/>
@@ -2567,6 +3025,8 @@
       <c r="E225" s="3" t="n"/>
       <c r="F225" s="3" t="n"/>
       <c r="G225" s="3" t="n"/>
+      <c r="H225" s="3" t="n"/>
+      <c r="I225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n"/>
@@ -2576,6 +3036,8 @@
       <c r="E226" s="3" t="n"/>
       <c r="F226" s="3" t="n"/>
       <c r="G226" s="3" t="n"/>
+      <c r="H226" s="3" t="n"/>
+      <c r="I226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n"/>
@@ -2585,6 +3047,8 @@
       <c r="E227" s="3" t="n"/>
       <c r="F227" s="3" t="n"/>
       <c r="G227" s="3" t="n"/>
+      <c r="H227" s="3" t="n"/>
+      <c r="I227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n"/>
@@ -2594,6 +3058,8 @@
       <c r="E228" s="3" t="n"/>
       <c r="F228" s="3" t="n"/>
       <c r="G228" s="3" t="n"/>
+      <c r="H228" s="3" t="n"/>
+      <c r="I228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n"/>
@@ -2603,6 +3069,8 @@
       <c r="E229" s="3" t="n"/>
       <c r="F229" s="3" t="n"/>
       <c r="G229" s="3" t="n"/>
+      <c r="H229" s="3" t="n"/>
+      <c r="I229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n"/>
@@ -2612,6 +3080,8 @@
       <c r="E230" s="3" t="n"/>
       <c r="F230" s="3" t="n"/>
       <c r="G230" s="3" t="n"/>
+      <c r="H230" s="3" t="n"/>
+      <c r="I230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n"/>
@@ -2621,6 +3091,8 @@
       <c r="E231" s="3" t="n"/>
       <c r="F231" s="3" t="n"/>
       <c r="G231" s="3" t="n"/>
+      <c r="H231" s="3" t="n"/>
+      <c r="I231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n"/>
@@ -2630,6 +3102,8 @@
       <c r="E232" s="3" t="n"/>
       <c r="F232" s="3" t="n"/>
       <c r="G232" s="3" t="n"/>
+      <c r="H232" s="3" t="n"/>
+      <c r="I232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n"/>
@@ -2639,6 +3113,8 @@
       <c r="E233" s="3" t="n"/>
       <c r="F233" s="3" t="n"/>
       <c r="G233" s="3" t="n"/>
+      <c r="H233" s="3" t="n"/>
+      <c r="I233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n"/>
@@ -2648,6 +3124,8 @@
       <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
       <c r="G234" s="3" t="n"/>
+      <c r="H234" s="3" t="n"/>
+      <c r="I234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n"/>
@@ -2657,6 +3135,8 @@
       <c r="E235" s="3" t="n"/>
       <c r="F235" s="3" t="n"/>
       <c r="G235" s="3" t="n"/>
+      <c r="H235" s="3" t="n"/>
+      <c r="I235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n"/>
@@ -2666,6 +3146,8 @@
       <c r="E236" s="3" t="n"/>
       <c r="F236" s="3" t="n"/>
       <c r="G236" s="3" t="n"/>
+      <c r="H236" s="3" t="n"/>
+      <c r="I236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n"/>
@@ -2675,6 +3157,8 @@
       <c r="E237" s="3" t="n"/>
       <c r="F237" s="3" t="n"/>
       <c r="G237" s="3" t="n"/>
+      <c r="H237" s="3" t="n"/>
+      <c r="I237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n"/>
@@ -2684,6 +3168,8 @@
       <c r="E238" s="3" t="n"/>
       <c r="F238" s="3" t="n"/>
       <c r="G238" s="3" t="n"/>
+      <c r="H238" s="3" t="n"/>
+      <c r="I238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n"/>
@@ -2693,6 +3179,8 @@
       <c r="E239" s="3" t="n"/>
       <c r="F239" s="3" t="n"/>
       <c r="G239" s="3" t="n"/>
+      <c r="H239" s="3" t="n"/>
+      <c r="I239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n"/>
@@ -2702,6 +3190,8 @@
       <c r="E240" s="3" t="n"/>
       <c r="F240" s="3" t="n"/>
       <c r="G240" s="3" t="n"/>
+      <c r="H240" s="3" t="n"/>
+      <c r="I240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n"/>
@@ -2711,6 +3201,8 @@
       <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="n"/>
       <c r="G241" s="3" t="n"/>
+      <c r="H241" s="3" t="n"/>
+      <c r="I241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n"/>
@@ -2720,6 +3212,8 @@
       <c r="E242" s="3" t="n"/>
       <c r="F242" s="3" t="n"/>
       <c r="G242" s="3" t="n"/>
+      <c r="H242" s="3" t="n"/>
+      <c r="I242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n"/>
@@ -2729,6 +3223,8 @@
       <c r="E243" s="3" t="n"/>
       <c r="F243" s="3" t="n"/>
       <c r="G243" s="3" t="n"/>
+      <c r="H243" s="3" t="n"/>
+      <c r="I243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n"/>
@@ -2738,6 +3234,8 @@
       <c r="E244" s="3" t="n"/>
       <c r="F244" s="3" t="n"/>
       <c r="G244" s="3" t="n"/>
+      <c r="H244" s="3" t="n"/>
+      <c r="I244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n"/>
@@ -2747,6 +3245,8 @@
       <c r="E245" s="3" t="n"/>
       <c r="F245" s="3" t="n"/>
       <c r="G245" s="3" t="n"/>
+      <c r="H245" s="3" t="n"/>
+      <c r="I245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n"/>
@@ -2756,6 +3256,8 @@
       <c r="E246" s="3" t="n"/>
       <c r="F246" s="3" t="n"/>
       <c r="G246" s="3" t="n"/>
+      <c r="H246" s="3" t="n"/>
+      <c r="I246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n"/>
@@ -2765,6 +3267,8 @@
       <c r="E247" s="3" t="n"/>
       <c r="F247" s="3" t="n"/>
       <c r="G247" s="3" t="n"/>
+      <c r="H247" s="3" t="n"/>
+      <c r="I247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n"/>
@@ -2774,6 +3278,8 @@
       <c r="E248" s="3" t="n"/>
       <c r="F248" s="3" t="n"/>
       <c r="G248" s="3" t="n"/>
+      <c r="H248" s="3" t="n"/>
+      <c r="I248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n"/>
@@ -2783,6 +3289,8 @@
       <c r="E249" s="3" t="n"/>
       <c r="F249" s="3" t="n"/>
       <c r="G249" s="3" t="n"/>
+      <c r="H249" s="3" t="n"/>
+      <c r="I249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n"/>
@@ -2792,6 +3300,8 @@
       <c r="E250" s="3" t="n"/>
       <c r="F250" s="3" t="n"/>
       <c r="G250" s="3" t="n"/>
+      <c r="H250" s="3" t="n"/>
+      <c r="I250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n"/>
@@ -2801,6 +3311,8 @@
       <c r="E251" s="3" t="n"/>
       <c r="F251" s="3" t="n"/>
       <c r="G251" s="3" t="n"/>
+      <c r="H251" s="3" t="n"/>
+      <c r="I251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n"/>
@@ -2810,6 +3322,8 @@
       <c r="E252" s="3" t="n"/>
       <c r="F252" s="3" t="n"/>
       <c r="G252" s="3" t="n"/>
+      <c r="H252" s="3" t="n"/>
+      <c r="I252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n"/>
@@ -2819,6 +3333,8 @@
       <c r="E253" s="3" t="n"/>
       <c r="F253" s="3" t="n"/>
       <c r="G253" s="3" t="n"/>
+      <c r="H253" s="3" t="n"/>
+      <c r="I253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n"/>
@@ -2828,6 +3344,8 @@
       <c r="E254" s="3" t="n"/>
       <c r="F254" s="3" t="n"/>
       <c r="G254" s="3" t="n"/>
+      <c r="H254" s="3" t="n"/>
+      <c r="I254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n"/>
@@ -2837,6 +3355,8 @@
       <c r="E255" s="3" t="n"/>
       <c r="F255" s="3" t="n"/>
       <c r="G255" s="3" t="n"/>
+      <c r="H255" s="3" t="n"/>
+      <c r="I255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n"/>
@@ -2846,6 +3366,8 @@
       <c r="E256" s="3" t="n"/>
       <c r="F256" s="3" t="n"/>
       <c r="G256" s="3" t="n"/>
+      <c r="H256" s="3" t="n"/>
+      <c r="I256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n"/>
@@ -2855,6 +3377,8 @@
       <c r="E257" s="3" t="n"/>
       <c r="F257" s="3" t="n"/>
       <c r="G257" s="3" t="n"/>
+      <c r="H257" s="3" t="n"/>
+      <c r="I257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n"/>
@@ -2864,6 +3388,8 @@
       <c r="E258" s="3" t="n"/>
       <c r="F258" s="3" t="n"/>
       <c r="G258" s="3" t="n"/>
+      <c r="H258" s="3" t="n"/>
+      <c r="I258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n"/>
@@ -2873,6 +3399,8 @@
       <c r="E259" s="3" t="n"/>
       <c r="F259" s="3" t="n"/>
       <c r="G259" s="3" t="n"/>
+      <c r="H259" s="3" t="n"/>
+      <c r="I259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n"/>
@@ -2882,6 +3410,8 @@
       <c r="E260" s="3" t="n"/>
       <c r="F260" s="3" t="n"/>
       <c r="G260" s="3" t="n"/>
+      <c r="H260" s="3" t="n"/>
+      <c r="I260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n"/>
@@ -2891,6 +3421,8 @@
       <c r="E261" s="3" t="n"/>
       <c r="F261" s="3" t="n"/>
       <c r="G261" s="3" t="n"/>
+      <c r="H261" s="3" t="n"/>
+      <c r="I261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n"/>
@@ -2900,6 +3432,8 @@
       <c r="E262" s="3" t="n"/>
       <c r="F262" s="3" t="n"/>
       <c r="G262" s="3" t="n"/>
+      <c r="H262" s="3" t="n"/>
+      <c r="I262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n"/>
@@ -2909,6 +3443,8 @@
       <c r="E263" s="3" t="n"/>
       <c r="F263" s="3" t="n"/>
       <c r="G263" s="3" t="n"/>
+      <c r="H263" s="3" t="n"/>
+      <c r="I263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n"/>
@@ -2918,6 +3454,8 @@
       <c r="E264" s="3" t="n"/>
       <c r="F264" s="3" t="n"/>
       <c r="G264" s="3" t="n"/>
+      <c r="H264" s="3" t="n"/>
+      <c r="I264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n"/>
@@ -2927,6 +3465,8 @@
       <c r="E265" s="3" t="n"/>
       <c r="F265" s="3" t="n"/>
       <c r="G265" s="3" t="n"/>
+      <c r="H265" s="3" t="n"/>
+      <c r="I265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n"/>
@@ -2936,6 +3476,8 @@
       <c r="E266" s="3" t="n"/>
       <c r="F266" s="3" t="n"/>
       <c r="G266" s="3" t="n"/>
+      <c r="H266" s="3" t="n"/>
+      <c r="I266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n"/>
@@ -2945,6 +3487,8 @@
       <c r="E267" s="3" t="n"/>
       <c r="F267" s="3" t="n"/>
       <c r="G267" s="3" t="n"/>
+      <c r="H267" s="3" t="n"/>
+      <c r="I267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n"/>
@@ -2954,6 +3498,8 @@
       <c r="E268" s="3" t="n"/>
       <c r="F268" s="3" t="n"/>
       <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
+      <c r="I268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n"/>
@@ -2963,6 +3509,8 @@
       <c r="E269" s="3" t="n"/>
       <c r="F269" s="3" t="n"/>
       <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="n"/>
+      <c r="I269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n"/>
@@ -2972,6 +3520,8 @@
       <c r="E270" s="3" t="n"/>
       <c r="F270" s="3" t="n"/>
       <c r="G270" s="3" t="n"/>
+      <c r="H270" s="3" t="n"/>
+      <c r="I270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n"/>
@@ -2981,6 +3531,8 @@
       <c r="E271" s="3" t="n"/>
       <c r="F271" s="3" t="n"/>
       <c r="G271" s="3" t="n"/>
+      <c r="H271" s="3" t="n"/>
+      <c r="I271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n"/>
@@ -2990,6 +3542,8 @@
       <c r="E272" s="3" t="n"/>
       <c r="F272" s="3" t="n"/>
       <c r="G272" s="3" t="n"/>
+      <c r="H272" s="3" t="n"/>
+      <c r="I272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n"/>
@@ -2999,6 +3553,8 @@
       <c r="E273" s="3" t="n"/>
       <c r="F273" s="3" t="n"/>
       <c r="G273" s="3" t="n"/>
+      <c r="H273" s="3" t="n"/>
+      <c r="I273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n"/>
@@ -3008,6 +3564,8 @@
       <c r="E274" s="3" t="n"/>
       <c r="F274" s="3" t="n"/>
       <c r="G274" s="3" t="n"/>
+      <c r="H274" s="3" t="n"/>
+      <c r="I274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n"/>
@@ -3017,6 +3575,8 @@
       <c r="E275" s="3" t="n"/>
       <c r="F275" s="3" t="n"/>
       <c r="G275" s="3" t="n"/>
+      <c r="H275" s="3" t="n"/>
+      <c r="I275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n"/>
@@ -3026,6 +3586,8 @@
       <c r="E276" s="3" t="n"/>
       <c r="F276" s="3" t="n"/>
       <c r="G276" s="3" t="n"/>
+      <c r="H276" s="3" t="n"/>
+      <c r="I276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n"/>
@@ -3035,6 +3597,8 @@
       <c r="E277" s="3" t="n"/>
       <c r="F277" s="3" t="n"/>
       <c r="G277" s="3" t="n"/>
+      <c r="H277" s="3" t="n"/>
+      <c r="I277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n"/>
@@ -3044,6 +3608,8 @@
       <c r="E278" s="3" t="n"/>
       <c r="F278" s="3" t="n"/>
       <c r="G278" s="3" t="n"/>
+      <c r="H278" s="3" t="n"/>
+      <c r="I278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n"/>
@@ -3053,6 +3619,8 @@
       <c r="E279" s="3" t="n"/>
       <c r="F279" s="3" t="n"/>
       <c r="G279" s="3" t="n"/>
+      <c r="H279" s="3" t="n"/>
+      <c r="I279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n"/>
@@ -3062,6 +3630,8 @@
       <c r="E280" s="3" t="n"/>
       <c r="F280" s="3" t="n"/>
       <c r="G280" s="3" t="n"/>
+      <c r="H280" s="3" t="n"/>
+      <c r="I280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="n"/>
@@ -3071,6 +3641,8 @@
       <c r="E281" s="3" t="n"/>
       <c r="F281" s="3" t="n"/>
       <c r="G281" s="3" t="n"/>
+      <c r="H281" s="3" t="n"/>
+      <c r="I281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n"/>
@@ -3080,6 +3652,8 @@
       <c r="E282" s="3" t="n"/>
       <c r="F282" s="3" t="n"/>
       <c r="G282" s="3" t="n"/>
+      <c r="H282" s="3" t="n"/>
+      <c r="I282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n"/>
@@ -3089,6 +3663,8 @@
       <c r="E283" s="3" t="n"/>
       <c r="F283" s="3" t="n"/>
       <c r="G283" s="3" t="n"/>
+      <c r="H283" s="3" t="n"/>
+      <c r="I283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n"/>
@@ -3098,6 +3674,8 @@
       <c r="E284" s="3" t="n"/>
       <c r="F284" s="3" t="n"/>
       <c r="G284" s="3" t="n"/>
+      <c r="H284" s="3" t="n"/>
+      <c r="I284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="n"/>
@@ -3107,6 +3685,8 @@
       <c r="E285" s="3" t="n"/>
       <c r="F285" s="3" t="n"/>
       <c r="G285" s="3" t="n"/>
+      <c r="H285" s="3" t="n"/>
+      <c r="I285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n"/>
@@ -3116,6 +3696,8 @@
       <c r="E286" s="3" t="n"/>
       <c r="F286" s="3" t="n"/>
       <c r="G286" s="3" t="n"/>
+      <c r="H286" s="3" t="n"/>
+      <c r="I286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n"/>
@@ -3125,6 +3707,8 @@
       <c r="E287" s="3" t="n"/>
       <c r="F287" s="3" t="n"/>
       <c r="G287" s="3" t="n"/>
+      <c r="H287" s="3" t="n"/>
+      <c r="I287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n"/>
@@ -3134,6 +3718,8 @@
       <c r="E288" s="3" t="n"/>
       <c r="F288" s="3" t="n"/>
       <c r="G288" s="3" t="n"/>
+      <c r="H288" s="3" t="n"/>
+      <c r="I288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n"/>
@@ -3143,6 +3729,8 @@
       <c r="E289" s="3" t="n"/>
       <c r="F289" s="3" t="n"/>
       <c r="G289" s="3" t="n"/>
+      <c r="H289" s="3" t="n"/>
+      <c r="I289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n"/>
@@ -3152,6 +3740,8 @@
       <c r="E290" s="3" t="n"/>
       <c r="F290" s="3" t="n"/>
       <c r="G290" s="3" t="n"/>
+      <c r="H290" s="3" t="n"/>
+      <c r="I290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n"/>
@@ -3161,6 +3751,8 @@
       <c r="E291" s="3" t="n"/>
       <c r="F291" s="3" t="n"/>
       <c r="G291" s="3" t="n"/>
+      <c r="H291" s="3" t="n"/>
+      <c r="I291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n"/>
@@ -3170,6 +3762,8 @@
       <c r="E292" s="3" t="n"/>
       <c r="F292" s="3" t="n"/>
       <c r="G292" s="3" t="n"/>
+      <c r="H292" s="3" t="n"/>
+      <c r="I292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n"/>
@@ -3179,6 +3773,8 @@
       <c r="E293" s="3" t="n"/>
       <c r="F293" s="3" t="n"/>
       <c r="G293" s="3" t="n"/>
+      <c r="H293" s="3" t="n"/>
+      <c r="I293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n"/>
@@ -3188,6 +3784,8 @@
       <c r="E294" s="3" t="n"/>
       <c r="F294" s="3" t="n"/>
       <c r="G294" s="3" t="n"/>
+      <c r="H294" s="3" t="n"/>
+      <c r="I294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n"/>
@@ -3197,6 +3795,8 @@
       <c r="E295" s="3" t="n"/>
       <c r="F295" s="3" t="n"/>
       <c r="G295" s="3" t="n"/>
+      <c r="H295" s="3" t="n"/>
+      <c r="I295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n"/>
@@ -3206,6 +3806,8 @@
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="3" t="n"/>
+      <c r="H296" s="3" t="n"/>
+      <c r="I296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n"/>
@@ -3215,6 +3817,8 @@
       <c r="E297" s="3" t="n"/>
       <c r="F297" s="3" t="n"/>
       <c r="G297" s="3" t="n"/>
+      <c r="H297" s="3" t="n"/>
+      <c r="I297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n"/>
@@ -3224,6 +3828,8 @@
       <c r="E298" s="3" t="n"/>
       <c r="F298" s="3" t="n"/>
       <c r="G298" s="3" t="n"/>
+      <c r="H298" s="3" t="n"/>
+      <c r="I298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n"/>
@@ -3233,6 +3839,8 @@
       <c r="E299" s="3" t="n"/>
       <c r="F299" s="3" t="n"/>
       <c r="G299" s="3" t="n"/>
+      <c r="H299" s="3" t="n"/>
+      <c r="I299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n"/>
@@ -3242,6 +3850,8 @@
       <c r="E300" s="3" t="n"/>
       <c r="F300" s="3" t="n"/>
       <c r="G300" s="3" t="n"/>
+      <c r="H300" s="3" t="n"/>
+      <c r="I300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n"/>
@@ -3251,6 +3861,8 @@
       <c r="E301" s="3" t="n"/>
       <c r="F301" s="3" t="n"/>
       <c r="G301" s="3" t="n"/>
+      <c r="H301" s="3" t="n"/>
+      <c r="I301" s="3" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C301">
@@ -3271,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3281,6 +3893,8 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3447,190 +4061,171 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>有效期</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>除颤电极片、急救药品、氧气瓶等有保质期的，填到期日，格式 2027-03-15。
+设备本身没有有效期（如监护仪、呼吸机）就留空。
+⚠ 到期前系统会在手机端和后台首页自动提醒，这是「关键时刻拿出来发现过期」的唯一防线。</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>提醒提前天数</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>选填</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>到期前多少天开始提醒。留空或填 0 表示用默认的 30 天。
+药品效期短的可填小一点（如 14），电极片等可用默认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>填写示例（照这个格式填到第 1 张表）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>科室名称</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>设备品类</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>设备编码</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>设备名称</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>型号</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>急诊科</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>除颤仪</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>JZ-CD-01</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>除颤监护仪</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>飞利浦 HeartStart XL</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>抢救室</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>在用</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>急诊科</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>呼吸机</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>JZ-HX-01</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>转运呼吸机</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>迈瑞 TV-50</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>抢救室</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>在用</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>有效期</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>提醒提前天数</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>重症医学科</t>
+          <t>急诊科</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>监护仪</t>
+          <t>除颤仪</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>ICU-JH-01</t>
+          <t>JZ-CD-01</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>多参数监护仪</t>
+          <t>除颤监护仪</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>飞利浦 MX450</t>
+          <t>飞利浦 HeartStart XL</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>1 床</t>
+          <t>抢救室</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>在用</t>
         </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2027-03-15</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>重症医学科</t>
+          <t>急诊科</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>监护仪</t>
+          <t>呼吸机</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ICU-JH-02</t>
+          <t>JZ-HX-01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>多参数监护仪</t>
+          <t>转运呼吸机</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>飞利浦 MX450</t>
+          <t>迈瑞 TV-50</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2 床</t>
+          <t>抢救室</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3638,62 +4233,163 @@
           <t>在用</t>
         </is>
       </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>急诊科</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>药品</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>JZ-YP-01</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>肾上腺素注射液</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>1mg/支</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>抢救车</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>重症医学科</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>监护仪</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>ICU-JH-01</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>多参数监护仪</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>飞利浦 MX450</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>1 床</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>儿科</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>除颤仪</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>EK-CD-01</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>除颤监护仪（小儿电极）</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>卓尔 AED Pro</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>抢救室</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>在用</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>同一品类有多台时，序号顺延（JH-01、JH-02…），并在「位置」里写清楚区分（1 床 / 2 床）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>本表可以分科室分别填写，最后合并成一张再上传；也可以一个科室上传一次。</t>
-        </is>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>同一品类有多台时，序号顺延（JH-01、JH-02…），并在「位置」里写清楚区分（1 床 / 2 床）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>本表可以分科室分别填写，最后合并成一张再上传；也可以一个科室上传一次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>重复上传不会产生重复设备：编码相同的会被更新，编码新的才新增。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>有效期建议至少把「除颤电极片」和「急救药品」两类填上——这两类过期风险最高。</t>
         </is>
       </c>
     </row>

--- a/medops/docs/templates/2-设备表.xlsx
+++ b/medops/docs/templates/2-设备表.xlsx
@@ -3883,7 +3883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4057,7 +4057,9 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>在用 / 维修 / 停用 / 报废 四选一（有下拉可选）。留空默认为「在用」。只有「在用」的设备出现在日常巡检清单里，其余三种都不出现。</t>
+          <t>在用 / 维修 / 停用 / 报废 四选一（有下拉可选）。留空默认为「在用」。
+只有「在用」的设备出现在日常巡检清单和有效期提醒里，其余三种都不出现。
+⚠ 必须是这四个词，写「正常」「使用中」这类同义词会整行导入失败并提示。</t>
         </is>
       </c>
     </row>
@@ -4075,6 +4077,7 @@
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>除颤电极片、急救药品、氧气瓶等有保质期的，填到期日，格式 2027-03-15。
+必须年月日填全——只写 2027-03 会整行报错，系统不会替你猜成 3 月 1 号。
 设备本身没有有效期（如监护仪、呼吸机）就留空。
 ⚠ 到期前系统会在手机端和后台首页自动提醒，这是「关键时刻拿出来发现过期」的唯一防线。</t>
         </is>
@@ -4093,7 +4096,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>到期前多少天开始提醒。留空或填 0 表示用默认的 30 天。
+          <t>到期前多少天开始提醒，0～365 的整数。留空表示用默认的 30 天。
 药品效期短的可填小一点（如 14），电极片等可用默认。</t>
         </is>
       </c>
@@ -4390,6 +4393,20 @@
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>有效期建议至少把「除颤电极片」和「急救药品」两类填上——这两类过期风险最高。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 重新导入时，「有效期」「提醒提前天数」留空表示「本次不改动」，不会清掉系统里已录好的到期日；</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   要清空某台设备的有效期，请在该格填「无」。所以拿旧表格改改位置再传一次是安全的。</t>
         </is>
       </c>
     </row>
